--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CCE6F39-5218-4311-97EA-B262008D09CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F6AB68-2DB8-4A95-BD9D-E8F9622763E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,13 +835,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S04aH02,S02aH02,S03aH02</t>
+    <t>S02aH02,S04aH02,S03aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH03,S04aH03,S03aH01,S03aH03,S01aH03,S02aH01,S01aH01,S04aH01</t>
+    <t>S03aH01,S03aH03,S01aH03,S02aH01,S04aH03,S02aH03,S01aH01,S04aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -967,10 +967,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S02aH02,S01aH03,S05aH02,S05aH03,S03aH02,S04aH02,S07aH02,S03aH03,S01aH02,S04aH03,S02aH03,S07aH03,S06aH02,S06aH03</t>
+    <t>S06aH02,S06aH03,S03aH03,S04aH03,S04aH02,S01aH03,S05aH02,S05aH03,S02aH03,S07aH03,S03aH02,S01aH02,S07aH02,S02aH02</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S03aH01,S07aH04,S04aH05,S06aH01,S01aH04,S05aH01,S07aH06,S07aH05,S03aH04,S06aH06,S01aH05,S03aH06,S06aH05,S02aH06,S03aH05,S05aH05,S06aH04,S02aH01,S05aH06,S01aH01,S04aH01,S04aH06,S05aH04,S01aH06,S07aH01,S04aH04</t>
+    <t>S01aH06,S07aH01,S06aH06,S02aH01,S05aH06,S07aH05,S07aH04,S01aH01,S04aH01,S04aH06,S05aH04,S01aH04,S05aH01,S07aH06,S02aH04,S02aH05,S01aH05,S03aH06,S06aH05,S03aH04,S04aH05,S06aH01,S04aH04,S02aH06,S03aH05,S05aH05,S06aH04,S03aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1036,10 +1036,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,SaD,RaP,FaD,WaP,WaD,FaP,SaP</t>
+    <t>RaD,SaD,FaP,SaP,RaP,WaD,FaD,WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,WaP,SaN,WaN,RaP,FaN,RaN</t>
+    <t>FaP,SaP,SaN,WaN,RaP,WaP,FaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -24743,7 +24743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5616E4-114F-4C2A-892C-91F4B9BB2B76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF28A43D-CAA5-4690-809A-4F6A58DD8B46}">
   <dimension ref="A9:AN442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25233,7 +25233,7 @@
         <v>160</v>
       </c>
       <c r="AM14">
-        <v>0.4304722013836792</v>
+        <v>0.43047220138367925</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -25473,7 +25473,7 @@
         <v>158</v>
       </c>
       <c r="AM17">
-        <v>0.27894473618404597</v>
+        <v>0.27894473618404603</v>
       </c>
       <c r="AN17" t="s">
         <v>257</v>
@@ -26109,7 +26109,7 @@
         <v>160</v>
       </c>
       <c r="AM26">
-        <v>0.393175</v>
+        <v>0.39317499999999994</v>
       </c>
       <c r="AN26" t="s">
         <v>257</v>
@@ -26286,7 +26286,7 @@
         <v>158</v>
       </c>
       <c r="AM29">
-        <v>0.25462000000000001</v>
+        <v>0.25461999999999996</v>
       </c>
       <c r="AN29" t="s">
         <v>257</v>
@@ -26522,7 +26522,7 @@
         <v>158</v>
       </c>
       <c r="AM33">
-        <v>0.27854000000000001</v>
+        <v>0.27853999999999995</v>
       </c>
       <c r="AN33" t="s">
         <v>257</v>
@@ -26581,7 +26581,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.441575</v>
+        <v>0.44157500000000005</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -26781,7 +26781,7 @@
         <v>160</v>
       </c>
       <c r="AM38">
-        <v>0.424425</v>
+        <v>0.42442499999999994</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -27181,7 +27181,7 @@
         <v>160</v>
       </c>
       <c r="AM46">
-        <v>0.45515</v>
+        <v>0.45515000000000005</v>
       </c>
       <c r="AN46" t="s">
         <v>257</v>
@@ -27381,7 +27381,7 @@
         <v>160</v>
       </c>
       <c r="AM50">
-        <v>0.44527500000000003</v>
+        <v>0.44527499999999998</v>
       </c>
       <c r="AN50" t="s">
         <v>257</v>
@@ -27581,7 +27581,7 @@
         <v>160</v>
       </c>
       <c r="AM54">
-        <v>0.45067499999999999</v>
+        <v>0.45067499999999994</v>
       </c>
       <c r="AN54" t="s">
         <v>257</v>
@@ -27781,7 +27781,7 @@
         <v>160</v>
       </c>
       <c r="AM58">
-        <v>0.43355000000000005</v>
+        <v>0.43354999999999999</v>
       </c>
       <c r="AN58" t="s">
         <v>257</v>
@@ -28131,7 +28131,7 @@
         <v>158</v>
       </c>
       <c r="AM65">
-        <v>0.28386000000000006</v>
+        <v>0.28386</v>
       </c>
       <c r="AN65" t="s">
         <v>257</v>
@@ -28331,7 +28331,7 @@
         <v>158</v>
       </c>
       <c r="AM69">
-        <v>0.29122000000000003</v>
+        <v>0.29121999999999998</v>
       </c>
       <c r="AN69" t="s">
         <v>257</v>
@@ -28381,7 +28381,7 @@
         <v>160</v>
       </c>
       <c r="AM70">
-        <v>0.45214999999999994</v>
+        <v>0.45215</v>
       </c>
       <c r="AN70" t="s">
         <v>257</v>
@@ -28931,7 +28931,7 @@
         <v>158</v>
       </c>
       <c r="AM81">
-        <v>0.29471999999999998</v>
+        <v>0.29472000000000004</v>
       </c>
       <c r="AN81" t="s">
         <v>257</v>
@@ -28981,7 +28981,7 @@
         <v>160</v>
       </c>
       <c r="AM82">
-        <v>0.45582499999999998</v>
+        <v>0.45582500000000004</v>
       </c>
       <c r="AN82" t="s">
         <v>257</v>
@@ -29531,7 +29531,7 @@
         <v>158</v>
       </c>
       <c r="AM93">
-        <v>0.29891999999999996</v>
+        <v>0.29892000000000002</v>
       </c>
       <c r="AN93" t="s">
         <v>257</v>
@@ -29731,7 +29731,7 @@
         <v>158</v>
       </c>
       <c r="AM97">
-        <v>0.30503999999999998</v>
+        <v>0.30504000000000003</v>
       </c>
       <c r="AN97" t="s">
         <v>257</v>
@@ -29781,7 +29781,7 @@
         <v>160</v>
       </c>
       <c r="AM98">
-        <v>0.42627500000000002</v>
+        <v>0.42627499999999996</v>
       </c>
       <c r="AN98" t="s">
         <v>257</v>
@@ -30531,7 +30531,7 @@
         <v>158</v>
       </c>
       <c r="AM113">
-        <v>0.34518000000000004</v>
+        <v>0.34517999999999999</v>
       </c>
       <c r="AN113" t="s">
         <v>257</v>
@@ -30781,7 +30781,7 @@
         <v>160</v>
       </c>
       <c r="AM118">
-        <v>0.49807499999999999</v>
+        <v>0.49807500000000005</v>
       </c>
       <c r="AN118" t="s">
         <v>257</v>
@@ -30931,7 +30931,7 @@
         <v>158</v>
       </c>
       <c r="AM121">
-        <v>0.32473999999999997</v>
+        <v>0.32474000000000003</v>
       </c>
       <c r="AN121" t="s">
         <v>257</v>
@@ -38161,7 +38161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8CB2017-0210-4859-9DC8-FE744F918FA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F49BDD9-28CA-4D49-A2CF-4AD3B0A27762}">
   <dimension ref="A9:AN1522"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38918,7 +38918,7 @@
         <v>264</v>
       </c>
       <c r="AM17">
-        <v>0.4304722013836792</v>
+        <v>0.43047220138367914</v>
       </c>
       <c r="AN17" t="s">
         <v>257</v>
@@ -39478,7 +39478,7 @@
         <v>264</v>
       </c>
       <c r="AM24">
-        <v>0.4890285071267817</v>
+        <v>0.48902850712678164</v>
       </c>
       <c r="AN24" t="s">
         <v>257</v>
@@ -40598,7 +40598,7 @@
         <v>264</v>
       </c>
       <c r="AM38">
-        <v>0.393175</v>
+        <v>0.39317500000000005</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -42131,7 +42131,7 @@
         <v>264</v>
       </c>
       <c r="AM59">
-        <v>0.424425</v>
+        <v>0.42442499999999994</v>
       </c>
       <c r="AN59" t="s">
         <v>257</v>
@@ -42957,7 +42957,7 @@
         <v>264</v>
       </c>
       <c r="AM73">
-        <v>0.45515</v>
+        <v>0.45515000000000005</v>
       </c>
       <c r="AN73" t="s">
         <v>257</v>
@@ -43370,7 +43370,7 @@
         <v>264</v>
       </c>
       <c r="AM80">
-        <v>0.44527500000000003</v>
+        <v>0.44527499999999998</v>
       </c>
       <c r="AN80" t="s">
         <v>257</v>
@@ -43783,7 +43783,7 @@
         <v>264</v>
       </c>
       <c r="AM87">
-        <v>0.45067499999999999</v>
+        <v>0.45067500000000005</v>
       </c>
       <c r="AN87" t="s">
         <v>257</v>
@@ -44196,7 +44196,7 @@
         <v>264</v>
       </c>
       <c r="AM94">
-        <v>0.43355000000000005</v>
+        <v>0.43354999999999999</v>
       </c>
       <c r="AN94" t="s">
         <v>257</v>
@@ -45246,7 +45246,7 @@
         <v>264</v>
       </c>
       <c r="AM115">
-        <v>0.45214999999999994</v>
+        <v>0.45215</v>
       </c>
       <c r="AN115" t="s">
         <v>257</v>
@@ -47346,7 +47346,7 @@
         <v>264</v>
       </c>
       <c r="AM157">
-        <v>0.45839999999999997</v>
+        <v>0.45840000000000003</v>
       </c>
       <c r="AN157" t="s">
         <v>257</v>
@@ -47696,7 +47696,7 @@
         <v>264</v>
       </c>
       <c r="AM164">
-        <v>0.42627500000000002</v>
+        <v>0.42627499999999996</v>
       </c>
       <c r="AN164" t="s">
         <v>257</v>
@@ -49446,7 +49446,7 @@
         <v>264</v>
       </c>
       <c r="AM199">
-        <v>0.49807499999999999</v>
+        <v>0.49807500000000005</v>
       </c>
       <c r="AN199" t="s">
         <v>257</v>
@@ -49796,7 +49796,7 @@
         <v>264</v>
       </c>
       <c r="AM206">
-        <v>0.51842499999999991</v>
+        <v>0.51842500000000002</v>
       </c>
       <c r="AN206" t="s">
         <v>257</v>
@@ -82260,7 +82260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963D8110-0B99-4BF4-A30E-C508F6F74A61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12124603-393B-4F90-9807-2FA6C41EAF4D}">
   <dimension ref="A9:AN46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -82648,7 +82648,7 @@
         <v>297</v>
       </c>
       <c r="AM14">
-        <v>0.31121666666666664</v>
+        <v>0.3112166666666667</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -83100,7 +83100,7 @@
         <v>297</v>
       </c>
       <c r="AM24">
-        <v>0.3597083333333333</v>
+        <v>0.35970833333333335</v>
       </c>
       <c r="AN24" t="s">
         <v>257</v>
@@ -83366,7 +83366,7 @@
         <v>297</v>
       </c>
       <c r="AM31">
-        <v>0.37002500000000005</v>
+        <v>0.37002499999999999</v>
       </c>
       <c r="AN31" t="s">
         <v>257</v>
@@ -83404,7 +83404,7 @@
         <v>297</v>
       </c>
       <c r="AM32">
-        <v>0.36250833333333338</v>
+        <v>0.36250833333333327</v>
       </c>
       <c r="AN32" t="s">
         <v>257</v>
@@ -83442,7 +83442,7 @@
         <v>297</v>
       </c>
       <c r="AM33">
-        <v>0.35627499999999995</v>
+        <v>0.35627500000000006</v>
       </c>
       <c r="AN33" t="s">
         <v>257</v>
@@ -83756,7 +83756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13B3E674-AB8F-4DFC-B513-E40A34E6A0E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADBD312-FE26-419E-898A-BEC928DE5429}">
   <dimension ref="A9:AN442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84646,7 +84646,7 @@
         <v>300</v>
       </c>
       <c r="AM19">
-        <v>0.55555555555555547</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="AN19" t="s">
         <v>257</v>
@@ -85299,7 +85299,7 @@
         <v>303</v>
       </c>
       <c r="AM29">
-        <v>0.25073333333333331</v>
+        <v>0.25073333333333336</v>
       </c>
       <c r="AN29" t="s">
         <v>257</v>
@@ -85944,7 +85944,7 @@
         <v>303</v>
       </c>
       <c r="AM41">
-        <v>0.29656666666666665</v>
+        <v>0.2965666666666667</v>
       </c>
       <c r="AN41" t="s">
         <v>257</v>
@@ -87444,7 +87444,7 @@
         <v>300</v>
       </c>
       <c r="AM71">
-        <v>0.44393333333333329</v>
+        <v>0.44393333333333335</v>
       </c>
       <c r="AN71" t="s">
         <v>257</v>
@@ -87544,7 +87544,7 @@
         <v>303</v>
       </c>
       <c r="AM73">
-        <v>0.27833333333333332</v>
+        <v>0.27833333333333338</v>
       </c>
       <c r="AN73" t="s">
         <v>257</v>
@@ -87644,7 +87644,7 @@
         <v>300</v>
       </c>
       <c r="AM75">
-        <v>0.44749999999999995</v>
+        <v>0.44750000000000001</v>
       </c>
       <c r="AN75" t="s">
         <v>257</v>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F6AB68-2DB8-4A95-BD9D-E8F9622763E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE44C4A-316B-4744-81BC-20628E200B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,13 +835,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S04aH02,S03aH02,S01aH02</t>
+    <t>S04aH02,S01aH02,S03aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH03,S01aH03,S02aH01,S04aH03,S02aH03,S01aH01,S04aH01</t>
+    <t>S01aH03,S02aH01,S01aH01,S04aH01,S02aH03,S04aH03,S03aH01,S03aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -967,10 +967,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S06aH02,S06aH03,S03aH03,S04aH03,S04aH02,S01aH03,S05aH02,S05aH03,S02aH03,S07aH03,S03aH02,S01aH02,S07aH02,S02aH02</t>
+    <t>S02aH02,S02aH03,S07aH03,S03aH02,S04aH03,S07aH02,S03aH03,S01aH02,S01aH03,S05aH02,S05aH03,S04aH02,S06aH02,S06aH03</t>
   </si>
   <si>
-    <t>S01aH06,S07aH01,S06aH06,S02aH01,S05aH06,S07aH05,S07aH04,S01aH01,S04aH01,S04aH06,S05aH04,S01aH04,S05aH01,S07aH06,S02aH04,S02aH05,S01aH05,S03aH06,S06aH05,S03aH04,S04aH05,S06aH01,S04aH04,S02aH06,S03aH05,S05aH05,S06aH04,S03aH01</t>
+    <t>S03aH01,S01aH01,S04aH01,S04aH06,S05aH04,S02aH04,S02aH05,S01aH04,S05aH01,S07aH06,S02aH01,S05aH06,S03aH04,S06aH06,S01aH05,S03aH06,S06aH05,S04aH05,S06aH01,S02aH06,S03aH05,S05aH05,S06aH04,S07aH04,S07aH05,S01aH06,S07aH01,S04aH04</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1036,10 +1036,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,SaD,FaP,SaP,RaP,WaD,FaD,WaP</t>
+    <t>FaD,RaD,WaP,WaD,FaP,SaP,RaP,SaD</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,RaP,WaP,FaN,RaN</t>
+    <t>RaP,RaN,FaP,SaP,WaP,FaN,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24743,7 +24743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF28A43D-CAA5-4690-809A-4F6A58DD8B46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E8DBFA-420D-4DC9-BEB7-9A5BAF8D99FF}">
   <dimension ref="A9:AN442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25233,7 +25233,7 @@
         <v>160</v>
       </c>
       <c r="AM14">
-        <v>0.43047220138367925</v>
+        <v>0.4304722013836792</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -25473,7 +25473,7 @@
         <v>158</v>
       </c>
       <c r="AM17">
-        <v>0.27894473618404603</v>
+        <v>0.27894473618404597</v>
       </c>
       <c r="AN17" t="s">
         <v>257</v>
@@ -25793,7 +25793,7 @@
         <v>158</v>
       </c>
       <c r="AM21">
-        <v>0.31320330082520631</v>
+        <v>0.31320330082520625</v>
       </c>
       <c r="AN21" t="s">
         <v>257</v>
@@ -25873,7 +25873,7 @@
         <v>160</v>
       </c>
       <c r="AM22">
-        <v>0.5416979244811202</v>
+        <v>0.54169792448112031</v>
       </c>
       <c r="AN22" t="s">
         <v>257</v>
@@ -26050,7 +26050,7 @@
         <v>158</v>
       </c>
       <c r="AM25">
-        <v>0.24172000000000002</v>
+        <v>0.24171999999999999</v>
       </c>
       <c r="AN25" t="s">
         <v>257</v>
@@ -26109,7 +26109,7 @@
         <v>160</v>
       </c>
       <c r="AM26">
-        <v>0.39317499999999994</v>
+        <v>0.393175</v>
       </c>
       <c r="AN26" t="s">
         <v>257</v>
@@ -26286,7 +26286,7 @@
         <v>158</v>
       </c>
       <c r="AM29">
-        <v>0.25461999999999996</v>
+        <v>0.25462000000000001</v>
       </c>
       <c r="AN29" t="s">
         <v>257</v>
@@ -26522,7 +26522,7 @@
         <v>158</v>
       </c>
       <c r="AM33">
-        <v>0.27853999999999995</v>
+        <v>0.27854000000000001</v>
       </c>
       <c r="AN33" t="s">
         <v>257</v>
@@ -26581,7 +26581,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.44157500000000005</v>
+        <v>0.441575</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -26781,7 +26781,7 @@
         <v>160</v>
       </c>
       <c r="AM38">
-        <v>0.42442499999999994</v>
+        <v>0.424425</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -26981,7 +26981,7 @@
         <v>160</v>
       </c>
       <c r="AM42">
-        <v>0.44437499999999996</v>
+        <v>0.44437500000000002</v>
       </c>
       <c r="AN42" t="s">
         <v>257</v>
@@ -27181,7 +27181,7 @@
         <v>160</v>
       </c>
       <c r="AM46">
-        <v>0.45515000000000005</v>
+        <v>0.45515</v>
       </c>
       <c r="AN46" t="s">
         <v>257</v>
@@ -27381,7 +27381,7 @@
         <v>160</v>
       </c>
       <c r="AM50">
-        <v>0.44527499999999998</v>
+        <v>0.44527500000000003</v>
       </c>
       <c r="AN50" t="s">
         <v>257</v>
@@ -27581,7 +27581,7 @@
         <v>160</v>
       </c>
       <c r="AM54">
-        <v>0.45067499999999994</v>
+        <v>0.45067499999999999</v>
       </c>
       <c r="AN54" t="s">
         <v>257</v>
@@ -27781,7 +27781,7 @@
         <v>160</v>
       </c>
       <c r="AM58">
-        <v>0.43354999999999999</v>
+        <v>0.43355000000000005</v>
       </c>
       <c r="AN58" t="s">
         <v>257</v>
@@ -28131,7 +28131,7 @@
         <v>158</v>
       </c>
       <c r="AM65">
-        <v>0.28386</v>
+        <v>0.28386000000000006</v>
       </c>
       <c r="AN65" t="s">
         <v>257</v>
@@ -28381,7 +28381,7 @@
         <v>160</v>
       </c>
       <c r="AM70">
-        <v>0.45215</v>
+        <v>0.45214999999999994</v>
       </c>
       <c r="AN70" t="s">
         <v>257</v>
@@ -28931,7 +28931,7 @@
         <v>158</v>
       </c>
       <c r="AM81">
-        <v>0.29472000000000004</v>
+        <v>0.29471999999999998</v>
       </c>
       <c r="AN81" t="s">
         <v>257</v>
@@ -28981,7 +28981,7 @@
         <v>160</v>
       </c>
       <c r="AM82">
-        <v>0.45582500000000004</v>
+        <v>0.45582499999999998</v>
       </c>
       <c r="AN82" t="s">
         <v>257</v>
@@ -29531,7 +29531,7 @@
         <v>158</v>
       </c>
       <c r="AM93">
-        <v>0.29892000000000002</v>
+        <v>0.29891999999999996</v>
       </c>
       <c r="AN93" t="s">
         <v>257</v>
@@ -29731,7 +29731,7 @@
         <v>158</v>
       </c>
       <c r="AM97">
-        <v>0.30504000000000003</v>
+        <v>0.30503999999999998</v>
       </c>
       <c r="AN97" t="s">
         <v>257</v>
@@ -29781,7 +29781,7 @@
         <v>160</v>
       </c>
       <c r="AM98">
-        <v>0.42627499999999996</v>
+        <v>0.42627500000000002</v>
       </c>
       <c r="AN98" t="s">
         <v>257</v>
@@ -30781,7 +30781,7 @@
         <v>160</v>
       </c>
       <c r="AM118">
-        <v>0.49807500000000005</v>
+        <v>0.49807499999999999</v>
       </c>
       <c r="AN118" t="s">
         <v>257</v>
@@ -30931,7 +30931,7 @@
         <v>158</v>
       </c>
       <c r="AM121">
-        <v>0.32474000000000003</v>
+        <v>0.32473999999999997</v>
       </c>
       <c r="AN121" t="s">
         <v>257</v>
@@ -38161,7 +38161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F49BDD9-28CA-4D49-A2CF-4AD3B0A27762}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE616E40-EA4E-435E-B47D-2AB9D2A08127}">
   <dimension ref="A9:AN1522"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -39478,7 +39478,7 @@
         <v>264</v>
       </c>
       <c r="AM24">
-        <v>0.48902850712678164</v>
+        <v>0.4890285071267817</v>
       </c>
       <c r="AN24" t="s">
         <v>257</v>
@@ -40038,7 +40038,7 @@
         <v>264</v>
       </c>
       <c r="AM31">
-        <v>0.5416979244811202</v>
+        <v>0.54169792448112031</v>
       </c>
       <c r="AN31" t="s">
         <v>257</v>
@@ -41718,7 +41718,7 @@
         <v>264</v>
       </c>
       <c r="AM52">
-        <v>0.441575</v>
+        <v>0.44157500000000005</v>
       </c>
       <c r="AN52" t="s">
         <v>257</v>
@@ -42131,7 +42131,7 @@
         <v>264</v>
       </c>
       <c r="AM59">
-        <v>0.42442499999999994</v>
+        <v>0.424425</v>
       </c>
       <c r="AN59" t="s">
         <v>257</v>
@@ -42544,7 +42544,7 @@
         <v>264</v>
       </c>
       <c r="AM66">
-        <v>0.44437499999999996</v>
+        <v>0.44437500000000002</v>
       </c>
       <c r="AN66" t="s">
         <v>257</v>
@@ -42957,7 +42957,7 @@
         <v>264</v>
       </c>
       <c r="AM73">
-        <v>0.45515000000000005</v>
+        <v>0.45515</v>
       </c>
       <c r="AN73" t="s">
         <v>257</v>
@@ -44896,7 +44896,7 @@
         <v>264</v>
       </c>
       <c r="AM108">
-        <v>0.45424999999999999</v>
+        <v>0.45425000000000004</v>
       </c>
       <c r="AN108" t="s">
         <v>257</v>
@@ -45596,7 +45596,7 @@
         <v>264</v>
       </c>
       <c r="AM122">
-        <v>0.44895000000000002</v>
+        <v>0.44895000000000007</v>
       </c>
       <c r="AN122" t="s">
         <v>257</v>
@@ -46296,7 +46296,7 @@
         <v>264</v>
       </c>
       <c r="AM136">
-        <v>0.45582499999999998</v>
+        <v>0.45582500000000004</v>
       </c>
       <c r="AN136" t="s">
         <v>257</v>
@@ -46996,7 +46996,7 @@
         <v>264</v>
       </c>
       <c r="AM150">
-        <v>0.45905000000000001</v>
+        <v>0.45904999999999996</v>
       </c>
       <c r="AN150" t="s">
         <v>257</v>
@@ -50146,7 +50146,7 @@
         <v>264</v>
       </c>
       <c r="AM213">
-        <v>0.48444999999999994</v>
+        <v>0.48444999999999999</v>
       </c>
       <c r="AN213" t="s">
         <v>257</v>
@@ -82260,7 +82260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12124603-393B-4F90-9807-2FA6C41EAF4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687DEE6-3812-437B-9CD5-39CABE87CFB5}">
   <dimension ref="A9:AN46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -82489,7 +82489,7 @@
         <v>297</v>
       </c>
       <c r="AM11">
-        <v>0.34692581191274824</v>
+        <v>0.34692581191274829</v>
       </c>
       <c r="AN11" t="s">
         <v>257</v>
@@ -82648,7 +82648,7 @@
         <v>297</v>
       </c>
       <c r="AM14">
-        <v>0.3112166666666667</v>
+        <v>0.31121666666666664</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -82698,7 +82698,7 @@
         <v>297</v>
       </c>
       <c r="AM15">
-        <v>0.30836666666666668</v>
+        <v>0.30836666666666673</v>
       </c>
       <c r="AN15" t="s">
         <v>257</v>
@@ -82748,7 +82748,7 @@
         <v>297</v>
       </c>
       <c r="AM16">
-        <v>0.35940833333333333</v>
+        <v>0.35940833333333327</v>
       </c>
       <c r="AN16" t="s">
         <v>257</v>
@@ -83100,7 +83100,7 @@
         <v>297</v>
       </c>
       <c r="AM24">
-        <v>0.35970833333333335</v>
+        <v>0.3597083333333333</v>
       </c>
       <c r="AN24" t="s">
         <v>257</v>
@@ -83138,7 +83138,7 @@
         <v>297</v>
       </c>
       <c r="AM25">
-        <v>0.36224999999999996</v>
+        <v>0.36225000000000002</v>
       </c>
       <c r="AN25" t="s">
         <v>257</v>
@@ -83404,7 +83404,7 @@
         <v>297</v>
       </c>
       <c r="AM32">
-        <v>0.36250833333333327</v>
+        <v>0.36250833333333338</v>
       </c>
       <c r="AN32" t="s">
         <v>257</v>
@@ -83480,7 +83480,7 @@
         <v>297</v>
       </c>
       <c r="AM34">
-        <v>0.36396666666666661</v>
+        <v>0.36396666666666672</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -83518,7 +83518,7 @@
         <v>297</v>
       </c>
       <c r="AM35">
-        <v>0.35866666666666669</v>
+        <v>0.35866666666666663</v>
       </c>
       <c r="AN35" t="s">
         <v>257</v>
@@ -83620,7 +83620,7 @@
         <v>297</v>
       </c>
       <c r="AM38">
-        <v>0.41102500000000003</v>
+        <v>0.41102499999999997</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -83646,7 +83646,7 @@
         <v>297</v>
       </c>
       <c r="AM39">
-        <v>0.39924166666666672</v>
+        <v>0.39924166666666666</v>
       </c>
       <c r="AN39" t="s">
         <v>257</v>
@@ -83756,7 +83756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADBD312-FE26-419E-898A-BEC928DE5429}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B3E9A1-E7C8-4630-8115-7A32F9620977}">
   <dimension ref="A9:AN442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84074,7 +84074,7 @@
         <v>302</v>
       </c>
       <c r="AM12">
-        <v>0.26353810674890937</v>
+        <v>0.26353810674890943</v>
       </c>
       <c r="AN12" t="s">
         <v>257</v>
@@ -84246,7 +84246,7 @@
         <v>305</v>
       </c>
       <c r="AM14">
-        <v>0.3957886023229944</v>
+        <v>0.39578860232299445</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -84406,7 +84406,7 @@
         <v>302</v>
       </c>
       <c r="AM16">
-        <v>0.33529215637242643</v>
+        <v>0.33529215637242632</v>
       </c>
       <c r="AN16" t="s">
         <v>257</v>
@@ -84566,7 +84566,7 @@
         <v>305</v>
       </c>
       <c r="AM18">
-        <v>0.45792698174543628</v>
+        <v>0.45792698174543633</v>
       </c>
       <c r="AN18" t="s">
         <v>257</v>
@@ -84646,7 +84646,7 @@
         <v>300</v>
       </c>
       <c r="AM19">
-        <v>0.55555555555555558</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="AN19" t="s">
         <v>257</v>
@@ -84886,7 +84886,7 @@
         <v>305</v>
       </c>
       <c r="AM22">
-        <v>0.46626239893306654</v>
+        <v>0.46626239893306659</v>
       </c>
       <c r="AN22" t="s">
         <v>257</v>
@@ -85299,7 +85299,7 @@
         <v>303</v>
       </c>
       <c r="AM29">
-        <v>0.25073333333333336</v>
+        <v>0.25073333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>257</v>
@@ -85594,7 +85594,7 @@
         <v>305</v>
       </c>
       <c r="AM34">
-        <v>0.40736666666666665</v>
+        <v>0.40736666666666671</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -85944,7 +85944,7 @@
         <v>303</v>
       </c>
       <c r="AM41">
-        <v>0.2965666666666667</v>
+        <v>0.29656666666666665</v>
       </c>
       <c r="AN41" t="s">
         <v>257</v>
@@ -86094,7 +86094,7 @@
         <v>302</v>
       </c>
       <c r="AM44">
-        <v>0.29626666666666668</v>
+        <v>0.29626666666666662</v>
       </c>
       <c r="AN44" t="s">
         <v>257</v>
@@ -86494,7 +86494,7 @@
         <v>302</v>
       </c>
       <c r="AM52">
-        <v>0.31299999999999994</v>
+        <v>0.313</v>
       </c>
       <c r="AN52" t="s">
         <v>257</v>
@@ -86894,7 +86894,7 @@
         <v>302</v>
       </c>
       <c r="AM60">
-        <v>0.30333333333333329</v>
+        <v>0.30333333333333334</v>
       </c>
       <c r="AN60" t="s">
         <v>257</v>
@@ -87394,7 +87394,7 @@
         <v>305</v>
       </c>
       <c r="AM70">
-        <v>0.39810000000000006</v>
+        <v>0.39809999999999995</v>
       </c>
       <c r="AN70" t="s">
         <v>257</v>
@@ -87444,7 +87444,7 @@
         <v>300</v>
       </c>
       <c r="AM71">
-        <v>0.44393333333333335</v>
+        <v>0.44393333333333329</v>
       </c>
       <c r="AN71" t="s">
         <v>257</v>
@@ -87544,7 +87544,7 @@
         <v>303</v>
       </c>
       <c r="AM73">
-        <v>0.27833333333333338</v>
+        <v>0.27833333333333332</v>
       </c>
       <c r="AN73" t="s">
         <v>257</v>
@@ -87644,7 +87644,7 @@
         <v>300</v>
       </c>
       <c r="AM75">
-        <v>0.44750000000000001</v>
+        <v>0.44749999999999995</v>
       </c>
       <c r="AN75" t="s">
         <v>257</v>
@@ -87694,7 +87694,7 @@
         <v>302</v>
       </c>
       <c r="AM76">
-        <v>0.30349999999999999</v>
+        <v>0.30350000000000005</v>
       </c>
       <c r="AN76" t="s">
         <v>257</v>
@@ -87794,7 +87794,7 @@
         <v>305</v>
       </c>
       <c r="AM78">
-        <v>0.39606666666666662</v>
+        <v>0.39606666666666673</v>
       </c>
       <c r="AN78" t="s">
         <v>257</v>
@@ -88094,7 +88094,7 @@
         <v>302</v>
       </c>
       <c r="AM84">
-        <v>0.30883333333333329</v>
+        <v>0.30883333333333335</v>
       </c>
       <c r="AN84" t="s">
         <v>257</v>
@@ -89094,7 +89094,7 @@
         <v>302</v>
       </c>
       <c r="AM104">
-        <v>0.29646666666666666</v>
+        <v>0.29646666666666671</v>
       </c>
       <c r="AN104" t="s">
         <v>257</v>

--- a/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_NGA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE44C4A-316B-4744-81BC-20628E200B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B11971C1-4EB2-4138-8D95-43CF1FE16DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,13 +835,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S01aH02,S03aH02,S02aH02</t>
+    <t>S04aH02,S02aH02,S01aH02,S03aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH03,S02aH01,S01aH01,S04aH01,S02aH03,S04aH03,S03aH01,S03aH03</t>
+    <t>S01aH03,S02aH01,S01aH01,S04aH01,S04aH03,S02aH03,S03aH01,S03aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -967,10 +967,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S02aH02,S02aH03,S07aH03,S03aH02,S04aH03,S07aH02,S03aH03,S01aH02,S01aH03,S05aH02,S05aH03,S04aH02,S06aH02,S06aH03</t>
+    <t>S03aH03,S04aH03,S01aH02,S06aH02,S06aH03,S02aH03,S07aH03,S03aH02,S07aH02,S01aH03,S05aH02,S05aH03,S02aH02,S04aH02</t>
   </si>
   <si>
-    <t>S03aH01,S01aH01,S04aH01,S04aH06,S05aH04,S02aH04,S02aH05,S01aH04,S05aH01,S07aH06,S02aH01,S05aH06,S03aH04,S06aH06,S01aH05,S03aH06,S06aH05,S04aH05,S06aH01,S02aH06,S03aH05,S05aH05,S06aH04,S07aH04,S07aH05,S01aH06,S07aH01,S04aH04</t>
+    <t>S06aH06,S01aH04,S05aH01,S07aH06,S02aH01,S05aH06,S01aH05,S03aH06,S06aH05,S01aH06,S07aH01,S02aH04,S02aH05,S04aH05,S06aH01,S01aH01,S04aH01,S04aH06,S05aH04,S03aH04,S07aH04,S03aH01,S04aH04,S07aH05,S02aH06,S03aH05,S05aH05,S06aH04</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1036,10 +1036,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,RaD,WaP,WaD,FaP,SaP,RaP,SaD</t>
+    <t>FaD,FaP,SaP,RaP,WaD,SaD,RaD,WaP</t>
   </si>
   <si>
-    <t>RaP,RaN,FaP,SaP,WaP,FaN,SaN,WaN</t>
+    <t>RaP,FaN,SaN,WaN,WaP,FaP,SaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24743,7 +24743,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E8DBFA-420D-4DC9-BEB7-9A5BAF8D99FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B03A830A-7627-4F28-912D-346F399AB89C}">
   <dimension ref="A9:AN442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25553,7 +25553,7 @@
         <v>160</v>
       </c>
       <c r="AM18">
-        <v>0.4890285071267817</v>
+        <v>0.48902850712678164</v>
       </c>
       <c r="AN18" t="s">
         <v>257</v>
@@ -25793,7 +25793,7 @@
         <v>158</v>
       </c>
       <c r="AM21">
-        <v>0.31320330082520625</v>
+        <v>0.31320330082520631</v>
       </c>
       <c r="AN21" t="s">
         <v>257</v>
@@ -26581,7 +26581,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.441575</v>
+        <v>0.44157500000000005</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -26781,7 +26781,7 @@
         <v>160</v>
       </c>
       <c r="AM38">
-        <v>0.424425</v>
+        <v>0.42442499999999994</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -26981,7 +26981,7 @@
         <v>160</v>
       </c>
       <c r="AM42">
-        <v>0.44437500000000002</v>
+        <v>0.44437499999999996</v>
       </c>
       <c r="AN42" t="s">
         <v>257</v>
@@ -27181,7 +27181,7 @@
         <v>160</v>
       </c>
       <c r="AM46">
-        <v>0.45515</v>
+        <v>0.45515000000000005</v>
       </c>
       <c r="AN46" t="s">
         <v>257</v>
@@ -27381,7 +27381,7 @@
         <v>160</v>
       </c>
       <c r="AM50">
-        <v>0.44527500000000003</v>
+        <v>0.44527499999999998</v>
       </c>
       <c r="AN50" t="s">
         <v>257</v>
@@ -27531,7 +27531,7 @@
         <v>158</v>
       </c>
       <c r="AM53">
-        <v>0.29151999999999995</v>
+        <v>0.29152</v>
       </c>
       <c r="AN53" t="s">
         <v>257</v>
@@ -27581,7 +27581,7 @@
         <v>160</v>
       </c>
       <c r="AM54">
-        <v>0.45067499999999999</v>
+        <v>0.45067500000000005</v>
       </c>
       <c r="AN54" t="s">
         <v>257</v>
@@ -27781,7 +27781,7 @@
         <v>160</v>
       </c>
       <c r="AM58">
-        <v>0.43355000000000005</v>
+        <v>0.43354999999999999</v>
       </c>
       <c r="AN58" t="s">
         <v>257</v>
@@ -27981,7 +27981,7 @@
         <v>160</v>
       </c>
       <c r="AM62">
-        <v>0.44155</v>
+        <v>0.44154999999999994</v>
       </c>
       <c r="AN62" t="s">
         <v>257</v>
@@ -28381,7 +28381,7 @@
         <v>160</v>
       </c>
       <c r="AM70">
-        <v>0.45214999999999994</v>
+        <v>0.45215</v>
       </c>
       <c r="AN70" t="s">
         <v>257</v>
@@ -29581,7 +29581,7 @@
         <v>160</v>
       </c>
       <c r="AM94">
-        <v>0.45839999999999997</v>
+        <v>0.45840000000000003</v>
       </c>
       <c r="AN94" t="s">
         <v>257</v>
@@ -29781,7 +29781,7 @@
         <v>160</v>
       </c>
       <c r="AM98">
-        <v>0.42627500000000002</v>
+        <v>0.42627499999999996</v>
       </c>
       <c r="AN98" t="s">
         <v>257</v>
@@ -30781,7 +30781,7 @@
         <v>160</v>
       </c>
       <c r="AM118">
-        <v>0.49807499999999999</v>
+        <v>0.49807500000000005</v>
       </c>
       <c r="AN118" t="s">
         <v>257</v>
@@ -30981,7 +30981,7 @@
         <v>160</v>
       </c>
       <c r="AM122">
-        <v>0.51842499999999991</v>
+        <v>0.51842500000000002</v>
       </c>
       <c r="AN122" t="s">
         <v>257</v>
@@ -38161,7 +38161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE616E40-EA4E-435E-B47D-2AB9D2A08127}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477E3514-E60E-4E16-BA77-106471B81375}">
   <dimension ref="A9:AN1522"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38918,7 +38918,7 @@
         <v>264</v>
       </c>
       <c r="AM17">
-        <v>0.43047220138367914</v>
+        <v>0.43047220138367925</v>
       </c>
       <c r="AN17" t="s">
         <v>257</v>
@@ -40038,7 +40038,7 @@
         <v>264</v>
       </c>
       <c r="AM31">
-        <v>0.54169792448112031</v>
+        <v>0.5416979244811202</v>
       </c>
       <c r="AN31" t="s">
         <v>257</v>
@@ -40598,7 +40598,7 @@
         <v>264</v>
       </c>
       <c r="AM38">
-        <v>0.39317500000000005</v>
+        <v>0.39317499999999994</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -42131,7 +42131,7 @@
         <v>264</v>
       </c>
       <c r="AM59">
-        <v>0.424425</v>
+        <v>0.42442499999999994</v>
       </c>
       <c r="AN59" t="s">
         <v>257</v>
@@ -42544,7 +42544,7 @@
         <v>264</v>
       </c>
       <c r="AM66">
-        <v>0.44437500000000002</v>
+        <v>0.44437499999999996</v>
       </c>
       <c r="AN66" t="s">
         <v>257</v>
@@ -42957,7 +42957,7 @@
         <v>264</v>
       </c>
       <c r="AM73">
-        <v>0.45515</v>
+        <v>0.45515000000000005</v>
       </c>
       <c r="AN73" t="s">
         <v>257</v>
@@ -43783,7 +43783,7 @@
         <v>264</v>
       </c>
       <c r="AM87">
-        <v>0.45067500000000005</v>
+        <v>0.45067499999999994</v>
       </c>
       <c r="AN87" t="s">
         <v>257</v>
@@ -44896,7 +44896,7 @@
         <v>264</v>
       </c>
       <c r="AM108">
-        <v>0.45425000000000004</v>
+        <v>0.45424999999999999</v>
       </c>
       <c r="AN108" t="s">
         <v>257</v>
@@ -45596,7 +45596,7 @@
         <v>264</v>
       </c>
       <c r="AM122">
-        <v>0.44895000000000007</v>
+        <v>0.44895000000000002</v>
       </c>
       <c r="AN122" t="s">
         <v>257</v>
@@ -46996,7 +46996,7 @@
         <v>264</v>
       </c>
       <c r="AM150">
-        <v>0.45904999999999996</v>
+        <v>0.45905000000000001</v>
       </c>
       <c r="AN150" t="s">
         <v>257</v>
@@ -47346,7 +47346,7 @@
         <v>264</v>
       </c>
       <c r="AM157">
-        <v>0.45840000000000003</v>
+        <v>0.45839999999999997</v>
       </c>
       <c r="AN157" t="s">
         <v>257</v>
@@ -49796,7 +49796,7 @@
         <v>264</v>
       </c>
       <c r="AM206">
-        <v>0.51842500000000002</v>
+        <v>0.51842499999999991</v>
       </c>
       <c r="AN206" t="s">
         <v>257</v>
@@ -50146,7 +50146,7 @@
         <v>264</v>
       </c>
       <c r="AM213">
-        <v>0.48444999999999999</v>
+        <v>0.48444999999999994</v>
       </c>
       <c r="AN213" t="s">
         <v>257</v>
@@ -82260,7 +82260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687DEE6-3812-437B-9CD5-39CABE87CFB5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B354A437-3DDD-46EA-9732-9F3B5467E6D8}">
   <dimension ref="A9:AN46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -82489,7 +82489,7 @@
         <v>297</v>
       </c>
       <c r="AM11">
-        <v>0.34692581191274829</v>
+        <v>0.34692581191274824</v>
       </c>
       <c r="AN11" t="s">
         <v>257</v>
@@ -82548,7 +82548,7 @@
         <v>297</v>
       </c>
       <c r="AM12">
-        <v>0.38121509544052673</v>
+        <v>0.38121509544052684</v>
       </c>
       <c r="AN12" t="s">
         <v>257</v>
@@ -82648,7 +82648,7 @@
         <v>297</v>
       </c>
       <c r="AM14">
-        <v>0.31121666666666664</v>
+        <v>0.3112166666666667</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -82748,7 +82748,7 @@
         <v>297</v>
       </c>
       <c r="AM16">
-        <v>0.35940833333333327</v>
+        <v>0.35940833333333333</v>
       </c>
       <c r="AN16" t="s">
         <v>257</v>
@@ -82848,7 +82848,7 @@
         <v>297</v>
       </c>
       <c r="AM18">
-        <v>0.36326666666666663</v>
+        <v>0.36326666666666668</v>
       </c>
       <c r="AN18" t="s">
         <v>257</v>
@@ -83100,7 +83100,7 @@
         <v>297</v>
       </c>
       <c r="AM24">
-        <v>0.3597083333333333</v>
+        <v>0.35970833333333335</v>
       </c>
       <c r="AN24" t="s">
         <v>257</v>
@@ -83252,7 +83252,7 @@
         <v>297</v>
       </c>
       <c r="AM28">
-        <v>0.3637333333333333</v>
+        <v>0.36373333333333341</v>
       </c>
       <c r="AN28" t="s">
         <v>257</v>
@@ -83328,7 +83328,7 @@
         <v>297</v>
       </c>
       <c r="AM30">
-        <v>0.35862499999999997</v>
+        <v>0.35862500000000003</v>
       </c>
       <c r="AN30" t="s">
         <v>257</v>
@@ -83442,7 +83442,7 @@
         <v>297</v>
       </c>
       <c r="AM33">
-        <v>0.35627500000000006</v>
+        <v>0.35627499999999995</v>
       </c>
       <c r="AN33" t="s">
         <v>257</v>
@@ -83480,7 +83480,7 @@
         <v>297</v>
       </c>
       <c r="AM34">
-        <v>0.36396666666666672</v>
+        <v>0.36396666666666661</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -83518,7 +83518,7 @@
         <v>297</v>
       </c>
       <c r="AM35">
-        <v>0.35866666666666663</v>
+        <v>0.35866666666666669</v>
       </c>
       <c r="AN35" t="s">
         <v>257</v>
@@ -83620,7 +83620,7 @@
         <v>297</v>
       </c>
       <c r="AM38">
-        <v>0.41102499999999997</v>
+        <v>0.41102500000000003</v>
       </c>
       <c r="AN38" t="s">
         <v>257</v>
@@ -83646,7 +83646,7 @@
         <v>297</v>
       </c>
       <c r="AM39">
-        <v>0.39924166666666666</v>
+        <v>0.39924166666666672</v>
       </c>
       <c r="AN39" t="s">
         <v>257</v>
@@ -83756,7 +83756,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B3E9A1-E7C8-4630-8115-7A32F9620977}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE31BC56-28A3-4298-8A9A-FC856A757D6E}">
   <dimension ref="A9:AN442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84246,7 +84246,7 @@
         <v>305</v>
       </c>
       <c r="AM14">
-        <v>0.39578860232299445</v>
+        <v>0.3957886023229944</v>
       </c>
       <c r="AN14" t="s">
         <v>257</v>
@@ -84566,7 +84566,7 @@
         <v>305</v>
       </c>
       <c r="AM18">
-        <v>0.45792698174543633</v>
+        <v>0.45792698174543628</v>
       </c>
       <c r="AN18" t="s">
         <v>257</v>
@@ -84646,7 +84646,7 @@
         <v>300</v>
       </c>
       <c r="AM19">
-        <v>0.55555555555555547</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="AN19" t="s">
         <v>257</v>
@@ -84886,7 +84886,7 @@
         <v>305</v>
       </c>
       <c r="AM22">
-        <v>0.46626239893306659</v>
+        <v>0.46626239893306654</v>
       </c>
       <c r="AN22" t="s">
         <v>257</v>
@@ -85594,7 +85594,7 @@
         <v>305</v>
       </c>
       <c r="AM34">
-        <v>0.40736666666666671</v>
+        <v>0.40736666666666665</v>
       </c>
       <c r="AN34" t="s">
         <v>257</v>
@@ -87394,7 +87394,7 @@
         <v>305</v>
       </c>
       <c r="AM70">
-        <v>0.39809999999999995</v>
+        <v>0.39810000000000006</v>
       </c>
       <c r="AN70" t="s">
         <v>257</v>
@@ -87444,7 +87444,7 @@
         <v>300</v>
       </c>
       <c r="AM71">
-        <v>0.44393333333333329</v>
+        <v>0.44393333333333335</v>
       </c>
       <c r="AN71" t="s">
         <v>257</v>
@@ -87644,7 +87644,7 @@
         <v>300</v>
       </c>
       <c r="AM75">
-        <v>0.44749999999999995</v>
+        <v>0.44750000000000001</v>
       </c>
       <c r="AN75" t="s">
         <v>257</v>
@@ -87794,7 +87794,7 @@
         <v>305</v>
       </c>
       <c r="AM78">
-        <v>0.39606666666666673</v>
+        <v>0.39606666666666662</v>
       </c>
       <c r="AN78" t="s">
         <v>257</v>
